--- a/entity_plans/129 STATE DEPARTMENT FOR BROADCASTING AND TELECOMMUNICATIONS.xlsx
+++ b/entity_plans/129 STATE DEPARTMENT FOR BROADCASTING AND TELECOMMUNICATIONS.xlsx
@@ -8,6 +8,23 @@
   </bookViews>
   <sheets>
     <sheet name="Procurement Plan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="15" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="19" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="20" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="21" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="23" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="26" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="27" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +33,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;KES&quot; #,##0.00"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -97,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -122,6 +141,12 @@
     </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1675,4 +1700,6541 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Travel &amp; Food &amp; Lodging &amp; Entertainment Services — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>9011160101</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>CONFERENCE CENTERS</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>10800000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>9011160101</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>CONFERENCE CENTERS</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>1175000</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>4700000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr"/>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>9014150301</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>EXHIBITIONS</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr"/>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>9011160101</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>CONFERENCE CENTERS</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>64000</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>640000</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr"/>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>9010160301</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>CATERING SERVICES</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>600000</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>9011160101</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>CONFERENCE CENTERS</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>600000</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr"/>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>9011160101</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>CONFERENCE CENTERS</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>480000</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr"/>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>9011160101</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>CONFERENCE CENTERS</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>56300</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>450400</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr"/>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>9010160301</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>CATERING SERVICES</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>112500</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>450000</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>9010160301</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>CATERING SERVICES</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>100000</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>9011160101</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>CONFERENCE CENTERS</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>100000</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr"/>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>9011160101</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>CONFERENCE CENTERS</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>100000</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>9011160101</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>CONFERENCE CENTERS</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr"/>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="61" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Engineering &amp; Research &amp; Technology Based Services — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>8111180301</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>NETWORK INSTALLATION AND MAINTENANCE WORKS</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>10080000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>30240000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>8111180301</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>NETWORK INSTALLATION AND MAINTENANCE WORKS</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>10080000</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>20160000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr"/>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>81112209</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Development software maintenance</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>6666666</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>13333332</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr"/>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>8111210101</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>INTERNET SERVICE PROVIDERS ISP</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>571428</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>1714284</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>81112306</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Printer, scanner and multifunctional equipment maintenance</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>81112307</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>PC or workstation or notebook maintenance</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>60000</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>240000</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>81112602</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Laptop and desktop computer depot repair service</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>56000</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>224000</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Military &amp; Private Vehicles &amp; their Accessories &amp; Components — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>2517250445</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>TYRE FORKLIFT 6</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>1746666</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>17466660</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>2517250445</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>TYRE FORKLIFT 6</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>80.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>34000</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>2720000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>2517250445</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>TYRE FORKLIFT 6</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>38121</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>1524840</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>25191549</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Catering service unit </t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>225000</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>900000</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>25191549</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Catering service unit </t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>480000</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>480000</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Service Industry Machinery &amp; Equipment &amp; Supplies — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>4810171102</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>WATER DISPENSERS</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>27777</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>277770</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Domestic Appliances &amp; Supplies &amp; Consumer Electronic Products — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>52161551</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Wireless microphone and instrument amplification system</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>142684</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>2853680</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>52161611</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Microphone stand</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>226004</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>2260040</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>5216150501</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>TELEVISIONS</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>78125</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>390625</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Furniture &amp; Furnishings — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>56101522</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Arm chair</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>72.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>55356</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>3985632</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>56101720</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Office or work chair</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>72.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>55356</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>3985632</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>56112102</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Task seating</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>27777</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>1388850</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>56112102</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Task seating</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>21333</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>1066650</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>56101720</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Office or work chair</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>27777</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>416655</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>56101720</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Office or work chair</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>16775</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>335500</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>5610153201</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>FURNITURE SET</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>27777</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>277770</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>5610170203</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>CABINET RECORD FIRE RESISTANT</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>21333</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>213330</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="115" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Industrial Cleaning Services — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>7611150104</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>OFFICE CLEANING, INCLUDING HOOVERING OF ALL THE CARPETS AND SCRUBBING OF CORRIDORS, WASHROOMS, STAIRS AND FLOORS</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>1541400</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>6165600</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Management &amp; Business Professionals &amp; Administrative Services — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>8014160701</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>EVENTS MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>300000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>80101606</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Project monitoring and evaluation</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>200000</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>800000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>80131502</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Commercial or industrial facility rental</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>240000</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>240000</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Education &amp; Training Services — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>8614170401</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>LIBRARY SUBSCRIPTION RENEWALS</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>75000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>300000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Paper Materials &amp; Products — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>1411151414</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>NOTEBOOKS SHORTHAND</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>142684</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>14268400</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>14111509</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Stationery</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>1333</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>266600</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>RFQ PWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>14111509</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Stationery</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>1000.00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>254</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>254000</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Power Generation &amp; Distribution Machinery &amp; Accessories — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>2611170101</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>RECHARGEABLE BATTERIES</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>142684</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>14268400</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>2611170101</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>RECHARGEABLE BATTERIES</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>142684</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>14268400</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>2611170101</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>RECHARGEABLE BATTERIES</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>16775</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>251625</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>2611171001</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>BATTERY</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>38121</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>228726</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Information Technology Broadcasting &amp; Telecommunications — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>4320200506</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>FLASH DISK 8GB</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>142684</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>15695240</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>43201827</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Portable hard disk storage device</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>226004</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>11300200</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>4323260501</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>ANALYTICAL OR SCIENTIFIC SOFTWARE</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>6666666</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>6666666</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr"/>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>4321150303</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>NOTEBOOK COMPUTERS</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>200000</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr"/>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>43211521</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>All in one desktop computer</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr"/>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>4321150303</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>NOTEBOOK COMPUTERS</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>571428</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>2857140</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>4321150701</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>WORKSTATIONS</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>55356</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>1383900</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>4321150701</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>WORKSTATIONS</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>103645</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>1243740</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>4321150801</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>DESKTOP COMPUTERS</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>78125</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>937500</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>4321150701</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>WORKSTATIONS</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>37037</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>925925</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>4321150802</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>PERSONAL COMPUTERS</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>37037</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>925925</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>4321150302</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>LAPTOP COMPUTERS</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>78125</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>625000</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>43212110</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Multi function printers</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>43232112</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Desktop publishing software</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>91500</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>366000</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Office Equipment &amp; Accessories &amp; Supplies — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>4412150604</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>ENVELOPES MANILA A4</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>1500.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>192</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>288000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ PWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>4410350201</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>COVER BINDING</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>4412150619</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>ENVELOPES CLASSIC</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>4412210403</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>PAPER CLIP LARGE</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Printing &amp; Photographic &amp; Audio &amp; Visual Equipment &amp; Supplies — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>4512150103</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>STILL CAMERAS</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>142684</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>5707360</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>4512150103</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>STILL CAMERAS</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>16.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>251562</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>4024992</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>45121603</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Camera lens</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>571428</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>2857140</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>45121516</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Digital camcorders or video cameras</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>142684</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>2853680</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>45111707</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Audio equipment connector and stage box</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>55356</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>2767800</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>45121602</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Camera tripods</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>55356</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>1107120</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>45121603</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Camera lens</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>571428</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>571428</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>4512150401</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>DIGITAL CAMERAS</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>100000</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Published Products — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>55121503</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Identification tags</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>600.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>350</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>210000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Editorial &amp; Design &amp; Graphic &amp; Fine Art Services — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>82121505</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Promotional or advertising printing</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>640000000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>82121505</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Promotional or advertising printing</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>165000</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>660000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>8213160301</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>VIDEO PRODUCTION SERVICES</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>165000</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>660000</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>82121505</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Promotional or advertising printing</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>142000</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>568000</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Storage &amp; Mail Services — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>7818150701</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>VEHICLE MECHANICAL REPAIR AND MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>1746666</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>5239998</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>7811150203</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>LOCAL AIR TRAVEL</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>7811150201</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>COMMERCIAL AIRPLANE TRAVEL</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>560000</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>1680000</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>7811150203</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>LOCAL AIR TRAVEL</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>34666</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>1039980</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>7818150701</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>VEHICLE MECHANICAL REPAIR AND MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>34000</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>1020000</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr"/>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>7811150201</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>COMMERCIAL AIRPLANE TRAVEL</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>18000</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>900000</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>7811150201</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>COMMERCIAL AIRPLANE TRAVEL</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>800000</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>7811150201</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>COMMERCIAL AIRPLANE TRAVEL</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>7680</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>768000</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>7818150701</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>VEHICLE MECHANICAL REPAIR AND MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>38121</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>762420</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr"/>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>7811150203</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>LOCAL AIR TRAVEL</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>60000</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>600000</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>7811150203</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>LOCAL AIR TRAVEL</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>600000</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>7818150701</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Automotive and light truck maintenance and repair</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Works</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>11300</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>452000</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr"/>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>7818150701</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>VEHICLE MECHANICAL REPAIR AND MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>91800</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>367200</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr"/>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>7818150701</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>VEHICLE MECHANICAL REPAIR AND MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>360000</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr"/>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>7811150203</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>LOCAL AIR TRAVEL</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>23000</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>230000</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>